--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F1F810C-55F4-49F1-AAAF-FA5328284E2C}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F27FDA-2BF3-440A-895A-0822D3C26E0B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$1:$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Packing List</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>8481.90.3000</t>
-  </si>
-  <si>
-    <t>UPS</t>
   </si>
   <si>
     <t xml:space="preserve">From  : </t>
@@ -195,14 +192,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$USD]\ 0.00"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.0000_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -315,6 +313,12 @@
       <name val="BatangChe"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -517,9 +521,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -640,63 +647,69 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -706,45 +719,40 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
@@ -816,14 +824,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>71844</xdr:rowOff>
+      <xdr:colOff>430696</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>71845</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1149,23 +1157,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="37" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" style="37" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.6640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="37" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" style="37" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="37" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" style="37" customWidth="1"/>
     <col min="8" max="8" width="12.1640625" style="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" style="37" customWidth="1"/>
     <col min="10" max="10" width="14" style="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73"/>
+      <c r="A1" s="44"/>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
@@ -1181,7 +1189,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="48" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="45"/>
@@ -1203,13 +1211,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="24" t="s">
         <v>2</v>
       </c>
@@ -1221,13 +1229,13 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="75" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
-      <c r="E5" s="72"/>
+      <c r="E5" s="50"/>
       <c r="F5" s="24" t="s">
         <v>5</v>
       </c>
@@ -1239,61 +1247,61 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="75" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="78"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="52"/>
       <c r="G7" s="45"/>
       <c r="H7" s="45"/>
-      <c r="I7" s="72"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="79"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="53"/>
       <c r="G8" s="45"/>
       <c r="H8" s="45"/>
-      <c r="I8" s="72"/>
+      <c r="I8" s="50"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="79"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="53"/>
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
-      <c r="I9" s="72"/>
+      <c r="I9" s="50"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1302,94 +1310,90 @@
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="47"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="49" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="51"/>
-      <c r="H11" s="82" t="s">
+      <c r="G11" s="58"/>
+      <c r="H11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="77" t="s">
+      <c r="I11" s="51" t="s">
         <v>14</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="72"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="45"/>
-      <c r="I12" s="72"/>
+      <c r="I12" s="50"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="72"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="50"/>
       <c r="H13" s="45"/>
-      <c r="I13" s="72"/>
+      <c r="I13" s="50"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="58" t="s">
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="71">
+        <v>46030</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="17" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="67">
-        <v>46030</v>
-      </c>
-      <c r="E15" s="68"/>
-      <c r="F15" s="17" t="s">
-        <v>21</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="20"/>
       <c r="J15" s="1"/>
@@ -1407,50 +1411,50 @@
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="33" t="s">
+      <c r="F17" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="82"/>
+      <c r="I17" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63" t="s">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="35" t="s">
+      <c r="F18" s="35" t="s">
         <v>26</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>27</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="11"/>
       <c r="I18" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="57" t="s">
-        <v>40</v>
+      <c r="A19" s="74" t="s">
+        <v>39</v>
       </c>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -1469,8 +1473,8 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="57" t="s">
-        <v>41</v>
+      <c r="A20" s="74" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
@@ -1483,8 +1487,8 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="57" t="s">
-        <v>42</v>
+      <c r="A21" s="74" t="s">
+        <v>41</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -1497,8 +1501,8 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="57" t="s">
-        <v>43</v>
+      <c r="A22" s="74" t="s">
+        <v>42</v>
       </c>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -1511,8 +1515,8 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="57" t="s">
-        <v>44</v>
+      <c r="A23" s="74" t="s">
+        <v>43</v>
       </c>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -1525,8 +1529,8 @@
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="57" t="s">
-        <v>45</v>
+      <c r="A24" s="74" t="s">
+        <v>44</v>
       </c>
       <c r="B24" s="45"/>
       <c r="C24" s="45"/>
@@ -1539,8 +1543,8 @@
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>46</v>
+      <c r="A25" s="74" t="s">
+        <v>45</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -1553,8 +1557,8 @@
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="57" t="s">
-        <v>47</v>
+      <c r="A26" s="74" t="s">
+        <v>46</v>
       </c>
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
@@ -1567,90 +1571,60 @@
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
+      <c r="A27" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
       <c r="E27" s="39"/>
       <c r="F27" s="39">
         <f>SUM(F19:F26)</f>
         <v>0</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H27" s="39">
         <f>SUM(H19:H26)</f>
         <v>1</v>
       </c>
       <c r="I27" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
+      <c r="A28" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="80"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
       <c r="J28" s="8"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
       <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
+      <c r="A30" s="22"/>
       <c r="J30" s="8"/>
     </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="22"/>
       <c r="J31" s="8"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
@@ -1658,55 +1632,57 @@
       <c r="I32" s="22"/>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="48" t="s">
-        <v>32</v>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="72" t="s">
+        <v>29</v>
       </c>
       <c r="B33" s="45"/>
-      <c r="C33" s="48">
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="45"/>
+      <c r="C36" s="67">
         <v>8116409</v>
       </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="10"/>
-    </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="10"/>
-    </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
+      <c r="D36" s="45"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
@@ -1715,10 +1691,12 @@
       <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
+      <c r="A37" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="45"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="45"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
@@ -1727,10 +1705,12 @@
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
+      <c r="A38" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="45"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="45"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
@@ -1750,8 +1730,76 @@
       <c r="I39" s="9"/>
       <c r="J39" s="10"/>
     </row>
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="E2:H2"/>
@@ -1763,38 +1811,6 @@
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="H11:H14"/>
     <mergeCell ref="F11:G12"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F27FDA-2BF3-440A-895A-0822D3C26E0B}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89E2C0BF-145E-451D-8C7F-A721005D3CA6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$42</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$1:$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$I$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$1:$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Packing List</t>
   </si>
@@ -51,25 +51,10 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>515, 5th floor Leader’s Bldg, Jangmi-ro 42,</t>
-  </si>
-  <si>
-    <t>L/C No:</t>
-  </si>
-  <si>
-    <t>Bundang-gu, Seongnam-si, Gyeonggi-do, 13496, Korea</t>
-  </si>
-  <si>
     <t>Applicant(If other than consignee)</t>
   </si>
   <si>
-    <t>Tel : 82-31-768-8151  Fax: 82-31-768-8156</t>
-  </si>
-  <si>
     <t>Consigned to :</t>
-  </si>
-  <si>
-    <t>ASC Engineered Solutions 2001 Spring Road Suite 300 Oak Brook, IL 60523</t>
   </si>
   <si>
     <t xml:space="preserve">Vessel  Name or Flight No
@@ -118,9 +103,6 @@
     <t>(PCS)</t>
   </si>
   <si>
-    <t>(KG/PC)</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -160,45 +142,49 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>KGS</t>
+    <t>5350008920 BUSHING 17STAR FOR ABZ015/019</t>
+  </si>
+  <si>
+    <t>BODY/COVER O-RING FOR ABZ015/019</t>
+  </si>
+  <si>
+    <t>INDICATOR FOR ABZ006B-100B</t>
+  </si>
+  <si>
+    <t>Incoterms:</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>5350008920 BUSHING 17STAR FOR ABZ015/019</t>
-  </si>
-  <si>
-    <t>BODY/COVER O-RING FOR ABZ015/019</t>
-  </si>
-  <si>
-    <t>INDICATOR FOR ABZ006B-100B</t>
-  </si>
-  <si>
-    <t>INDICATOR FOR ABZ150B-250B</t>
-  </si>
-  <si>
-    <t>INDICATOR FOR ABZ300B-350B</t>
-  </si>
-  <si>
-    <t>WINDOW FOR ABZ006B-100B</t>
-  </si>
-  <si>
-    <t>WINDOW FOR ABZ150B-250B</t>
-  </si>
-  <si>
-    <t>WINDOW FOR ABZ300B-350B</t>
+    <t>515, 5th floor Leader’s Bldg, Jangmi-ro 42,
+Bundang-gu, Seongnam-si, Gyeonggi-do, 13496, Korea,
+Tel : 82-31-768-8151  Fax: 82-31-768-8156</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(KG)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Size</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>* This shipment does not contain any Solid Wood Packaging Material.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$USD]\ 0.00"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="0.0000_ "/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
     <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="#,##0.00&quot; KG&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -528,7 +514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -538,21 +524,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -571,9 +545,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -592,9 +563,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -637,27 +605,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -688,9 +641,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -702,10 +652,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -722,33 +671,82 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -829,9 +827,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>430696</xdr:colOff>
+      <xdr:colOff>331304</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>71845</xdr:rowOff>
+      <xdr:rowOff>71844</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1157,31 +1155,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="37" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="37" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="37" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="37" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="37" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="37" customWidth="1"/>
-    <col min="10" max="10" width="14" style="37" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="30" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="30" customWidth="1"/>
+    <col min="6" max="7" width="14.83203125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="16" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="30" customWidth="1"/>
+    <col min="10" max="10" width="14" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="A1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1189,12 +1186,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1210,610 +1207,554 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="56" t="s">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="24" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="12" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="17"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="75" t="s">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="65"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="24" t="s">
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="75" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="62"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="62"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="64" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="73" t="s">
+      <c r="G12" s="47"/>
+      <c r="H12" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="56" t="s">
+      <c r="I12" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="59" t="s">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="56" t="s">
+      <c r="B14" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="64" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="58"/>
-      <c r="H11" s="63" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="58">
+        <v>46030</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81">
+        <v>1</v>
+      </c>
+      <c r="F20" s="82"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85">
+        <v>0.01</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31">
+        <f>SUM(F20:F22)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="86">
+        <f>SUM(G20:G22)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31">
+        <f>SUM(I20:I22)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="79"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="16"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="16"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="16"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="16"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="16"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="16"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="78"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="71">
-        <v>46030</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="35" t="s">
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="B36" s="34"/>
+      <c r="C36" s="54">
+        <v>8116409</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="6">
-        <v>1</v>
-      </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="41">
-        <v>1</v>
-      </c>
-      <c r="I19" s="40">
-        <v>0.01</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="69" t="s">
+      <c r="B37" s="34"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39">
-        <f>SUM(F19:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="39">
-        <f>SUM(H19:H26)</f>
-        <v>1</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="65" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="67">
-        <v>8116409</v>
-      </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="10"/>
-    </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="67" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="10"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="6"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="10"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="6"/>
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="10"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="6"/>
     </row>
     <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="10"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A28:I28"/>
+  <mergeCells count="38">
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A5:E7"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="E2:H2"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="F7:I10"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="F7:I11"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.59055118110236227" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89E2C0BF-145E-451D-8C7F-A721005D3CA6}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC29281C-BE25-4EB2-A815-0A4C07A2D7E6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
     <numFmt numFmtId="178" formatCode="0.0000_ "/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
     <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="#,##0.00&quot; KG&quot;"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00&quot; KG&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -514,7 +514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -612,10 +612,110 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -636,16 +736,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -655,98 +745,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1156,46 +1159,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="30" customWidth="1"/>
-    <col min="6" max="7" width="14.83203125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="5.69921875" style="30" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.69921875" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.296875" style="30" customWidth="1"/>
+    <col min="6" max="7" width="14.796875" style="30" customWidth="1"/>
     <col min="8" max="8" width="16" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.69921875" style="30" customWidth="1"/>
     <col min="10" max="10" width="14" style="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="72"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1207,14 +1210,14 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="18" t="s">
         <v>2</v>
       </c>
@@ -1225,14 +1228,14 @@
       <c r="I4" s="17"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="62" t="s">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
       <c r="F5" s="32" t="s">
         <v>35</v>
       </c>
@@ -1241,154 +1244,154 @@
       <c r="I5" s="13"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="65"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="52" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="68"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="58"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="39"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="69"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="77"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="45" t="s">
+    <row r="8" spans="1:10" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="39"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="77"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="62"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="39"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="45"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="77"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="62"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="39"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="45"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="77"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="36"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="74"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="45" t="s">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="52" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="47"/>
-      <c r="H12" s="51" t="s">
+      <c r="G12" s="58"/>
+      <c r="H12" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" s="78" t="s">
         <v>9</v>
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="39"/>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="85"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="39"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="36"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="74"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="69" t="s">
+    <row r="16" spans="1:10" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="58">
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="61">
         <v>46030</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="12" t="s">
         <v>15</v>
       </c>
@@ -1399,7 +1402,7 @@
       <c r="I16" s="15"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -1411,13 +1414,13 @@
       <c r="I17" s="23"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="61" t="s">
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
       <c r="E18" s="27" t="s">
         <v>18</v>
       </c>
@@ -1435,13 +1438,13 @@
       </c>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
       <c r="E19" s="29" t="s">
         <v>20</v>
       </c>
@@ -1457,65 +1460,65 @@
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="70" t="s">
+    <row r="20" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="81">
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="33">
         <v>1</v>
       </c>
-      <c r="F20" s="82"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="85">
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37">
         <v>0.01</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="70" t="s">
+    <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="85"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="70" t="s">
+    <row r="22" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="85"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="56" t="s">
+    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31">
         <f>SUM(F20:F22)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="86">
+      <c r="G23" s="38">
         <f>SUM(G20:G22)</f>
         <v>0</v>
       </c>
@@ -1526,59 +1529,59 @@
       </c>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="78" t="s">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="77" t="s">
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -1590,13 +1593,13 @@
       <c r="I32" s="16"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="59" t="s">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -1604,13 +1607,13 @@
       <c r="I33" s="16"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59" t="s">
+    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="16"/>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
@@ -1618,13 +1621,13 @@
       <c r="I34" s="16"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="75" t="s">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
@@ -1632,15 +1635,15 @@
       <c r="I35" s="16"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="54" t="s">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="54">
+      <c r="B36" s="40"/>
+      <c r="C36" s="39">
         <v>8116409</v>
       </c>
-      <c r="D36" s="34"/>
+      <c r="D36" s="40"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1648,13 +1651,13 @@
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="54" t="s">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="34"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="40"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1662,13 +1665,13 @@
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="54" t="s">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="34"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1676,7 +1679,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1688,7 +1691,7 @@
       <c r="I39" s="5"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1700,7 +1703,7 @@
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -1714,16 +1717,18 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="F7:I11"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A19:D19"/>
@@ -1740,18 +1745,16 @@
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="F7:I11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC29281C-BE25-4EB2-A815-0A4C07A2D7E6}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E11963-0E2F-4E9A-AD9B-8587DBFE2BD4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -165,11 +165,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Size</t>
+    <t>* This shipment does not contain any Solid Wood Packaging Material.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>* This shipment does not contain any Solid Wood Packaging Material.</t>
+    <t>PO No.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -535,9 +535,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -630,21 +627,102 @@
     <xf numFmtId="181" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -670,86 +748,11 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1159,46 +1162,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="5.69921875" style="30" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.69921875" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.296875" style="30" customWidth="1"/>
-    <col min="6" max="7" width="14.796875" style="30" customWidth="1"/>
-    <col min="8" max="8" width="16" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.69921875" style="30" customWidth="1"/>
-    <col min="10" max="10" width="14" style="30" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="29" customWidth="1"/>
+    <col min="6" max="7" width="14.83203125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="16" style="29" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="14" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72"/>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1210,440 +1213,438 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="57" t="s">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="16"/>
+      <c r="H4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="17"/>
+      <c r="I4" s="16"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="32" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="13"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="84" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="72"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="58"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="52"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="69"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="77"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="44"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="57" t="s">
+    <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="44"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="77"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="69"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="44"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="77"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="69"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="44"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="74"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="84" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="58"/>
-      <c r="H12" s="83" t="s">
+      <c r="G12" s="52"/>
+      <c r="H12" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="78" t="s">
+      <c r="I12" s="45" t="s">
         <v>9</v>
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="77"/>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="58"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="77"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="74"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="61">
-        <v>46030</v>
-      </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="12" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="11" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="15"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="23"/>
+    <row r="17" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="65" t="s">
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="27" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="87" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="G18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="H18" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="27" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55" t="s">
+    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="29" t="s">
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="G19" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="H19" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="28" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86" t="s">
+    <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="33">
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="88">
         <v>1</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37">
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="36">
         <v>0.01</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86" t="s">
+    <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="36"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86" t="s">
+    <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31">
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30">
         <f>SUM(F20:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="38">
+        <v>1</v>
+      </c>
+      <c r="G23" s="37">
         <f>SUM(G20:G22)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31">
+      <c r="H23" s="30"/>
+      <c r="I23" s="30">
         <f>SUM(I20:I22)</f>
         <v>0.01</v>
       </c>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53" t="s">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="15"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="15"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="15"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="16"/>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="15"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="44" t="s">
+    <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="50" t="s">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="39" t="s">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="39">
+      <c r="B36" s="39"/>
+      <c r="C36" s="59">
         <v>8116409</v>
       </c>
-      <c r="D36" s="40"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1651,13 +1652,13 @@
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="39" t="s">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="40"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1665,13 +1666,13 @@
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="39" t="s">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="40"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1679,11 +1680,11 @@
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -1691,11 +1692,11 @@
       <c r="I39" s="5"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -1703,11 +1704,11 @@
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -1717,18 +1718,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="F7:I11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A19:D19"/>
@@ -1745,16 +1744,18 @@
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="F7:I11"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="11_C773ECE91B8FE9F859DF066E589C653E1B3496D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E11963-0E2F-4E9A-AD9B-8587DBFE2BD4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{EAA26186-71AB-4E44-AE3F-9E859F59102E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CE038F-8034-4979-80BA-9D13B95DC557}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t xml:space="preserve">HS CODE: </t>
   </si>
   <si>
-    <t>8481.90.3000</t>
-  </si>
-  <si>
     <t xml:space="preserve">From  : </t>
   </si>
   <si>
@@ -170,6 +167,10 @@
   </si>
   <si>
     <t>PO No.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>8481.90.0000</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -177,14 +178,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$USD]\ 0.00"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="0.0000_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="#,##0.00&quot; KG&quot;"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00&quot; KG&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -514,7 +514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -575,7 +575,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -584,7 +584,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -609,28 +609,128 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -651,16 +751,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -669,90 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1168,23 +1174,24 @@
     <col min="2" max="2" width="5.6640625" style="29" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="29" customWidth="1"/>
-    <col min="6" max="7" width="14.83203125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" style="29" customWidth="1"/>
     <col min="8" max="8" width="16" style="29" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" style="29" customWidth="1"/>
     <col min="10" max="10" width="14" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="A1" s="77"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1192,12 +1199,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1214,13 +1221,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="63"/>
       <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
@@ -1232,15 +1239,15 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="71"/>
+      <c r="A5" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="72"/>
       <c r="F5" s="31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -1248,157 +1255,157 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="72"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="57" t="s">
+      <c r="A6" s="73"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="52"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="63"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="44"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="82"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="82"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="69"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="44"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="82"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="69"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="44"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="82"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="41"/>
+      <c r="A11" s="52"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="79"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="57" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="52"/>
-      <c r="H12" s="56" t="s">
+      <c r="G12" s="63"/>
+      <c r="H12" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="45" t="s">
-        <v>9</v>
+      <c r="I12" s="83" t="s">
+        <v>39</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="58"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="44"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="82"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="44"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="82"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="41"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="68"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="79"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="11" t="s">
-        <v>15</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="1"/>
@@ -1416,132 +1423,129 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="87" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>18</v>
-      </c>
       <c r="G18" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="27" t="s">
+      <c r="I18" s="27" t="s">
         <v>29</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>30</v>
       </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28" t="s">
+      <c r="G19" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="37">
+        <v>1</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="88">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36">
-        <v>0.01</v>
-      </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="30">
+      <c r="F23" s="40">
         <f>SUM(F20:F22)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="41">
         <f>SUM(G20:G22)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30">
-        <f>SUM(I20:I22)</f>
-        <v>0.01</v>
-      </c>
+      <c r="H23" s="41"/>
+      <c r="I23" s="40"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
+      <c r="A24" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1565,17 +1569,17 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
+      <c r="A30" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1595,12 +1599,12 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
+      <c r="A33" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -1609,12 +1613,12 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
+      <c r="A34" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -1623,12 +1627,12 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
+      <c r="A35" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -1637,14 +1641,14 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="59">
+      <c r="A36" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="43"/>
+      <c r="C36" s="42">
         <v>8116409</v>
       </c>
-      <c r="D36" s="39"/>
+      <c r="D36" s="43"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1653,12 +1657,12 @@
       <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="39"/>
+      <c r="A37" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="43"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="43"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1667,12 +1671,12 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="39"/>
+      <c r="A38" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="43"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1718,16 +1722,18 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="F7:I11"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A19:D19"/>
@@ -1744,18 +1750,16 @@
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="F7:I11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeongtaek.Bang\OneDrive - Rotork plc\바탕 화면\업무\NOAH ACTUATION\noahAutomation\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{EAA26186-71AB-4E44-AE3F-9E859F59102E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CE038F-8034-4979-80BA-9D13B95DC557}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFB409-76BC-4F46-B485-6EB3092ED8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,12 +178,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="#,##0.00&quot; KG&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
@@ -630,34 +629,106 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="180" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -685,80 +756,8 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1183,15 +1182,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1199,12 +1198,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1221,13 +1220,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="63"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
       <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
@@ -1239,13 +1238,13 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="72"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="74"/>
       <c r="F5" s="31" t="s">
         <v>34</v>
       </c>
@@ -1255,151 +1254,151 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="73"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="89" t="s">
+      <c r="A6" s="75"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="63"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="55"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="74"/>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="82"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="47"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="82"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="82"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="47"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="82"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="47"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="79"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="44"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="89" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="88" t="s">
+      <c r="G12" s="55"/>
+      <c r="H12" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="83" t="s">
+      <c r="I12" s="48" t="s">
         <v>39</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90"/>
-      <c r="B13" s="87"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="82"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="47"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="82"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="47"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="79"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="44"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
       <c r="D16" s="66"/>
-      <c r="E16" s="67"/>
+      <c r="E16" s="58"/>
       <c r="F16" s="11" t="s">
         <v>14</v>
       </c>
@@ -1423,12 +1422,12 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="34" t="s">
         <v>38</v>
       </c>
@@ -1447,12 +1446,12 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
       <c r="E19" s="28"/>
       <c r="F19" s="36" t="s">
         <v>19</v>
@@ -1469,12 +1468,12 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
       <c r="E20" s="35"/>
       <c r="F20" s="37">
         <v>1</v>
@@ -1487,28 +1486,28 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
       <c r="E21" s="35"/>
-      <c r="F21" s="39"/>
+      <c r="F21" s="37"/>
       <c r="G21" s="38"/>
       <c r="H21" s="32"/>
       <c r="I21" s="33"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="39"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="38"/>
       <c r="H22" s="32"/>
       <c r="I22" s="33"/>
@@ -1522,30 +1521,30 @@
       <c r="C23" s="65"/>
       <c r="D23" s="65"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="40">
+      <c r="F23" s="90">
         <f>SUM(F20:F22)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="40">
         <f>SUM(G20:G22)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="41"/>
-      <c r="I23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1569,17 +1568,17 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="57" t="s">
+      <c r="A30" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1599,12 +1598,12 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -1613,12 +1612,12 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -1627,12 +1626,12 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -1641,14 +1640,14 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="42">
+      <c r="B36" s="42"/>
+      <c r="C36" s="62">
         <v>8116409</v>
       </c>
-      <c r="D36" s="43"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1657,12 +1656,12 @@
       <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="42" t="s">
+      <c r="A37" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="43"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1671,12 +1670,12 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="43"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="43"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1722,18 +1721,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="F7:I11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A19:D19"/>
@@ -1750,16 +1747,18 @@
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="F7:I11"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/templates/packing_list.xlsx
+++ b/templates/packing_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeongtaek.Bang\OneDrive - Rotork plc\바탕 화면\업무\NOAH ACTUATION\noahAutomation\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rotork-my.sharepoint.com/personal/jeongtaek_bang_rotork_com/Documents/바탕 화면/업무/NOAH ACTUATION/noahAutomation/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFB409-76BC-4F46-B485-6EB3092ED8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{FBBFB409-76BC-4F46-B485-6EB3092ED8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C58D87DE-140A-440A-9837-8BF6100AE1E7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>Other reference :</t>
   </si>
   <si>
-    <t xml:space="preserve">HS CODE: </t>
-  </si>
-  <si>
     <t xml:space="preserve">From  : </t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>Quantity</t>
-  </si>
-  <si>
-    <t>Electric Actuator</t>
   </si>
   <si>
     <t>(PCS)</t>
@@ -170,8 +164,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>8481.90.0000</t>
+    <t>Actuator and Parts</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>HS CODE</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -183,9 +183,9 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="#,##0.00&quot; KG&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00&quot; KG&quot;"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -301,6 +301,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -314,7 +320,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -505,6 +511,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -513,7 +528,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -632,9 +647,13 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -687,7 +706,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
@@ -696,9 +714,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -756,8 +771,17 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1166,13 +1190,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="29" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="29" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" style="29" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" style="29" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" style="29" customWidth="1"/>
@@ -1182,15 +1209,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="A1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1198,12 +1225,12 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
@@ -1220,13 +1247,13 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="17" t="s">
         <v>2</v>
       </c>
@@ -1239,14 +1266,14 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="72" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="73"/>
       <c r="C5" s="73"/>
       <c r="D5" s="73"/>
       <c r="E5" s="74"/>
       <c r="F5" s="31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -1259,12 +1286,12 @@
       <c r="C6" s="73"/>
       <c r="D6" s="73"/>
       <c r="E6" s="74"/>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="55"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="57"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1273,24 +1300,24 @@
       <c r="C7" s="77"/>
       <c r="D7" s="77"/>
       <c r="E7" s="78"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="47"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="47"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="49"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1299,10 +1326,10 @@
       <c r="C9" s="80"/>
       <c r="D9" s="80"/>
       <c r="E9" s="81"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="47"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="49"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1311,10 +1338,10 @@
       <c r="C10" s="80"/>
       <c r="D10" s="80"/>
       <c r="E10" s="81"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="47"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="49"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1323,88 +1350,84 @@
       <c r="C11" s="83"/>
       <c r="D11" s="83"/>
       <c r="E11" s="84"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="44"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="60" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="48" t="s">
-        <v>39</v>
-      </c>
+      <c r="G12" s="57"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="50"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="61"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="47"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="49"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="47"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="49"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="44"/>
+        <v>10</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="46"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="11" t="s">
         <v>13</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="1"/>
@@ -1423,57 +1446,61 @@
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>17</v>
-      </c>
       <c r="G18" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>29</v>
-      </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
+      <c r="A19" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="28"/>
       <c r="F19" s="36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="68" t="s">
-        <v>31</v>
+      <c r="A20" s="69" t="s">
+        <v>29</v>
       </c>
       <c r="B20" s="69"/>
       <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
+      <c r="D20" s="92" t="s">
+        <v>39</v>
+      </c>
       <c r="E20" s="35"/>
       <c r="F20" s="37">
         <v>1</v>
@@ -1486,12 +1513,12 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="68" t="s">
-        <v>32</v>
+      <c r="A21" s="69" t="s">
+        <v>30</v>
       </c>
       <c r="B21" s="69"/>
       <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
+      <c r="D21" s="92"/>
       <c r="E21" s="35"/>
       <c r="F21" s="37"/>
       <c r="G21" s="38"/>
@@ -1500,12 +1527,12 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="A22" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="92"/>
       <c r="E22" s="35"/>
       <c r="F22" s="37"/>
       <c r="G22" s="38"/>
@@ -1514,14 +1541,14 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
+      <c r="A23" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="93"/>
       <c r="E23" s="30"/>
-      <c r="F23" s="90">
+      <c r="F23" s="41">
         <f>SUM(F20:F22)</f>
         <v>1</v>
       </c>
@@ -1535,7 +1562,7 @@
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="88" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="89"/>
       <c r="C24" s="89"/>
@@ -1569,7 +1596,7 @@
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="87" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="87"/>
       <c r="C30" s="87"/>
@@ -1598,12 +1625,12 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
+      <c r="A33" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -1612,12 +1639,12 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
+      <c r="A34" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -1627,7 +1654,7 @@
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="86"/>
       <c r="C35" s="86"/>
@@ -1640,14 +1667,14 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="62">
+      <c r="A36" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="64">
         <v>8116409</v>
       </c>
-      <c r="D36" s="42"/>
+      <c r="D36" s="44"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -1656,12 +1683,12 @@
       <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="42"/>
+      <c r="A37" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="44"/>
       <c r="C37" s="70"/>
-      <c r="D37" s="42"/>
+      <c r="D37" s="44"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -1670,12 +1697,12 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="42"/>
+      <c r="A38" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="44"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -1722,7 +1749,6 @@
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A9:E9"/>
@@ -1731,20 +1757,21 @@
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A5:E7"/>
     <mergeCell ref="A1:I1"/>
@@ -1762,7 +1789,7 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
